--- a/光伏配储项目/电价数据/2026/明山站.xlsx
+++ b/光伏配储项目/电价数据/2026/明山站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.35001</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.84554</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.38029</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.40543</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.4040899999999999</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.33435</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31317</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.26636</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.08081999999999999</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.7225</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17869</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.28012</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25991</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.26441</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24921</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.46919</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.37939</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.6934199999999999</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.4353</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.44816</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29743</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.60753</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.59039</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.75878</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.18952</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.61802</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43935</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44682</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.68004</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.9334199999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.5342</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.25556</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.39158</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.14167</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.17044</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.36666</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.48136</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.48146</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.74317</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.7986599999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.25769</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.0277</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.9359299999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.82604</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.78879</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.53132</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.5009100000000001</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.48235</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.42726</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.43815</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.75029</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.93137</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.00607</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5217999999999999</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.53955</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5304</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.53052</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.5109900000000001</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.41232</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.49068</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38758</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.25654</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.22476</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.26593</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.39438</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38765</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.37809</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.47973</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30081</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.36414</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.51154</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.51738</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.70314</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.67161</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.88822</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.41067</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.7842</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.54825</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.45267</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.38026</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.40527</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.69394</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.41879</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.39118</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.9852300000000001</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.62813</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.81049</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.8717</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.23957</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.67236</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.1877</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.90715</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.2821</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.17091</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.35351</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.0923</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.15551</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.69712</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.04413</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.94601</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.03552</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.91052</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.14775</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.95051</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45925</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.90576</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.95124</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43556</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.45212</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38205</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33593</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5303600000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.5075299999999999</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.5124</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.4619</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42647</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37894</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39897</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.39288</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.37055</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.4446</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.46272</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37845</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.40852</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37609</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37634</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38301</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.40193</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.49484</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.4552</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.45427</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40421</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.12404</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.16373</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.26897</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.39609</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.08162999999999999</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.9281200000000001</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.7423099999999999</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.36472</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.7275700000000001</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.9322</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.92575</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.9081399999999999</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.9102899999999999</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.18389</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.90342</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.8837</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.87571</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.03939</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5581199999999999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.6249199999999999</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.82965</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.84033</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.7069800000000001</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.75549</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5375700000000001</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.89477</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.46134</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39647</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45557</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51806</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5275700000000001</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.6045199999999999</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.65303</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.66303</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.67177</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.36238</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.63697</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.69612</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.47387</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50974</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.65673</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.81525</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.79827</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.93867</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.47414</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.67153</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.4567</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5413600000000001</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.64067</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.8367</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.59161</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.96462</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.76807</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.63385</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.58469</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.7240700000000001</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.44458</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.46495</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34351</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.53964</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.5184299999999999</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.45623</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39923</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37508</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39677</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.37026</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46719</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36504</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36655</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35766</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39504</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.3984</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38326</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.3991</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42356</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44389</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.43805</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.5102</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.65516</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.45724</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.45615</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.28455</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.27617</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.6932999999999999</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.39033</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.42821</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.65218</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.5607300000000001</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.46654</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.4135</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.44415</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.51323</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.69745</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.49295</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.53971</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45071</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40539</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.50452</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.60566</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.51911</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.65495</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.55561</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.5260199999999999</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50276</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.47479</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.44994</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.43535</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.4308999999999999</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.36993</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.38638</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.34093</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37142</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37362</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.29821</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28665</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14181</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.01968</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.41456</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.41971</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.41443</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.42056</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.42877</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.28225</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.26719</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.25435</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.12167</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.42805</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.38609</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.11148</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26338</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.44927</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41795</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31298</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.39179</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.2863</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.28777</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.21507</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.22508</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.22006</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.27887</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.17374</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30192</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.14568</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.23534</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.16466</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.23795</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.19976</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.17642</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29228</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.15552</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30159</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.23789</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.2606</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.18348</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26098</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.09942000000000001</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04152</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00957</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20535</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04884</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27415</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.20346</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.5945900000000001</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.00558</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.0595</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.0577</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3133</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.29854</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.37212</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.43238</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38471</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.43597</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.46952</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.41838</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7866000000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88748</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18706</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8702000000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.6456499999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.56914</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49313</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44992</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20697</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45827</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.4231</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39188</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38407</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39377</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37252</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.30403</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44279</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.44357</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5632699999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60697</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.9175399999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.48555</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.27334</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.42201</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.5995900000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.86434</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.30398</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29014</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26152</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.36479</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.62287</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.46723</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.29926</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.40505</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28135</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29195</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30719</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29237</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.16232</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.2564</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.25537</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27109</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.2537</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.27555</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.28568</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.30655</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.29673</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.28835</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.28781</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.28879</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.28876</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.29116</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.28887</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.27949</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.31976</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.90258</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.36214</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.31418</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30584</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.28654</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.29826</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.29662</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29287</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.28896</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.29965</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.28587</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29165</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29093</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.28806</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.29566</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.28921</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.2914</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30199</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30201</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.56757</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.44552</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.31266</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.42056</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.46003</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.5530900000000001</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.40193</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.21624</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.39828</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.41998</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.28346</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30647</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.46629</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.46241</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.29784</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.23692</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.91418</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.67773</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.28246</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.75934</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.89211</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.70757</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.21356</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.22213</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.48297</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5423300000000001</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.49538</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.40772</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.44814</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.4217</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41532</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.4467</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.29614</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.45915</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.27763</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.28189</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39405</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.43115</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.28006</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.37957</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.29058</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39664</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.27908</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.4862</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.16242</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.28948</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.29026</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.30163</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.29194</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.41776</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.26898</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15678</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.28131</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.28393</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01093</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.28363</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.27989</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.29957</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29136</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30445</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.29683</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.28616</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.29386</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.4533</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.5824900000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.39368</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.30219</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.29255</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.27823</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.29044</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.26931</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.26841</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.26038</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.25596</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.15393</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30105</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.18006</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.16932</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.17318</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.16676</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.14043</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.23704</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.25953</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.25708</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.30472</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.14988</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.14837</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30214</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.29573</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.19071</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.1616</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.20205</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.18526</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.16687</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.27315</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.24708</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.27447</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.14581</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.28937</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.5414800000000001</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.14537</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.20822</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.48928</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.5232599999999999</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.37609</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.37881</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.36453</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.36293</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.28625</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.30821</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.37601</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26703</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27655</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.38956</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.40892</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.37645</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.38585</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.28575</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.27512</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.28238</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.28543</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.29397</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.27189</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.26848</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.29343</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.29362</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.29713</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.28373</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.28595</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.27838</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.28406</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.28857</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.28343</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.28776</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.28654</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.27854</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.28274</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.2838</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.41358</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.36901</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.27486</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.27743</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.2368</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.27278</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.28318</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.28366</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.2908</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.29433</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.29298</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.28966</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.29847</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.29742</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.29589</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.28752</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.28905</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.28906</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.29241</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.28905</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.2884</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.28945</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.2884</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.2825</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.28623</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.29239</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.29617</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.28468</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29044</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.29828</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30272</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.32671</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28027</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.29739</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31615</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28342</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.29129</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.39003</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.33628</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28383</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30145</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29239</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.61265</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29773</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.40764</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.28059</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28105</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.27428</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.38557</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36221</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.29572</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.37427</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.45818</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.29356</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.35572</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.27575</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30078</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30175</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.29909</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.29833</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.30032</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.27063</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.28927</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.30218</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.29753</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.27671</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.28395</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.27791</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.28558</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.28644</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29107</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.29271</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.28685</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.28906</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.28904</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.28737</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.28817</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.2886</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.27719</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.29937</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30491</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.2894</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.29744</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.41358</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.19371</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.7054900000000001</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.50856</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.47942</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.37908</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.44951</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.51564</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38764</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.43931</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.37837</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.57797</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27502</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.29038</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.41598</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24486</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.38633</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.7387</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.47255</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.4401600000000001</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.41819</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.40299</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.5637300000000001</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.42493</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.4147</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.45417</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.44243</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.40837</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.44718</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.37504</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.67555</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.47494</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.43018</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.45016</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.71692</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.22507</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.47913</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22896</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.29958</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.26739</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.27595</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.19423</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.29716</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.26898</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.27671</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27103</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.27088</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.26744</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.17906</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.17207</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.26696</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.26825</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.26688</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.26714</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.26734</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.26695</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.17367</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29127</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.17121</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.1307</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.22381</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28605</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.28923</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.25362</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.17095</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.17681</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.21113</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.18244</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.14219</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.13455</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.22591</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.28563</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.30342</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.29141</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.29589</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.27291</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.29131</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.29277</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.28447</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.28998</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.25092</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.28973</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29267</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.28363</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.29471</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.29208</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.2827</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.2819</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.2694</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.27713</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.28181</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.22739</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.29012</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.29599</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.29335</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.29937</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.29298</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.2353</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.2789700000000001</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.25758</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.27707</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.26189</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.27457</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.27166</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.27623</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.21618</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.26457</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.20409</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.15159</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31583</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.28617</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.27152</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.28109</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.27689</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.26516</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.27834</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.27159</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29042</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.27555</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.30564</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.27477</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.27841</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.26409</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.27722</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.28171</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.28115</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.27238</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.26683</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.27537</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.28646</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.26625</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.27768</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.26531</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.28664</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29564</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31523</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.29873</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30428</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30197</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.30822</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40493</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6333</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.5002300000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.18221</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29029</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.37721</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.27244</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.29935</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.39005</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.39318</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.38279</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.43841</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.41098</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.38086</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.40836</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38716</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.30596</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.4361</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.48349</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.66576</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.62212</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6688999999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.2973</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.5046700000000001</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.44945</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.30186</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.30291</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.31243</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.30811</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.30489</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.30867</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.30335</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.30616</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.2958</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.2954</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.29841</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.27207</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.29029</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.29702</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.28064</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.25923</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.27652</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.25975</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.28311</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.28526</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.29377</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44204</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.40351</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.41191</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.45242</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.49029</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.5308099999999999</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.56517</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40059</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.38787</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40622</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.42346</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6756599999999999</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40403</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.83008</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39242</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.59963</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.41533</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.35334</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.43952</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.49621</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.36702</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.29491</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.29733</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.29411</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.27125</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.24888</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.26399</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.28698</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.29666</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.28568</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.28248</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.75079</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.59884</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.63849</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.29968</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.29518</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.29514</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.29841</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.29962</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.4005</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.24062</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.27187</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.27564</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.29745</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.26271</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.27345</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.26077</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.26837</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.28127</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.38824</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.39454</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.40676</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.38292</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38814</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.40336</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.42318</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.38943</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.37869</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40735</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.39092</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.42249</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.42851</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.41394</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.30616</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.41771</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.51148</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.45349</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.36657</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.29003</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.30244</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.21556</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38352</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.21802</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.21319</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.23745</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.27219</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.26528</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.22607</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.26614</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.28825</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.27846</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.16601</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.28874</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.16477</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.17157</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.20794</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.17413</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.28271</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.2571</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.21175</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.25708</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.19967</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.1419</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.24952</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.14218</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.18017</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.14093</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.13271</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.13668</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.17632</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.13463</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.13703</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.13943</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.14183</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.15145</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.16335</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.12607</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.27937</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.2818</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.5999800000000001</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.41093</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28166</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.99448</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.00528</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.31392</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.4126</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.44395</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.43262</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29925</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28039</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.29343</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.30368</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.23465</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.26009</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.28567</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.29843</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28703</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.25333</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.27646</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.26458</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.25972</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.19819</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.22991</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.21034</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.22713</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.25832</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.28603</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.24456</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.23937</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.15479</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.16136</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.24447</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.14531</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.27122</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.14806</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.22761</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.21611</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.28072</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.2747</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.27113</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.27399</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.26379</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.0008900000000000001</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.16548</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.16278</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26001</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.18812</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.2112</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.20216</v>
+      </c>
+      <c r="P136" t="n">
+        <v>-0.00484</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.18261</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.15834</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.04109</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24074</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.00247</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.01052</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.16001</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02212</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01369</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04299</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04090999999999999</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02937</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04316</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00371</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27994</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04928</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03546</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.008369999999999999</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03508</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20951</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27052</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29516</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28333</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.28073</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29241</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.29047</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29302</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.27623</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29159</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28568</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.31391</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30365</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29467</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29765</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28522</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29571</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.25882</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.27322</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.27306</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.28466</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.25951</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.28574</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.26169</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.26565</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.14428</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.14066</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.14464</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.14231</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.13875</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.12887</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41115</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.16629</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.26578</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.21418</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.22652</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85424</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86313</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.08563999999999999</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28336</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29468</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.28517</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.6378400000000001</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29664</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29552</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06998</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30299</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25452</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.4758</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.60203</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.5101</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.31763</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.7654099999999999</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9729</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.60237</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.82973</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.82796</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.83235</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9329400000000001</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.39757</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.29872</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.27786</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.47146</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.28174</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.27267</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.25091</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35328</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.24682</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.16429</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.24711</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.24043</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.23445</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.19835</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.22402</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.18287</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.14308</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.17878</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.13818</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.1406</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.12799</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.15623</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.21034</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.29038</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.25401</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.22272</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.23078</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.2423</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.26742</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.28783</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.30155</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37407</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.2855</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.27266</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30874</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25877</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33653</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.38805</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33397</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39434</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.30074</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.25656</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.30126</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.30257</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.30678</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.29853</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.28791</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.28159</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.28304</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.30591</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.30584</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.2958</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.29562</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.28764</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29175</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.29409</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.29417</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.29969</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.29562</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.30485</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.28614</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.5816399999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.27871</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.4377799999999999</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.2985</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30196</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29494</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.46538</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.42723</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.48179</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.11345</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.84304</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.8350700000000001</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40929</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.40134</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.54927</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.6811200000000001</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.89116</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.40509</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.5682200000000001</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.41894</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.19465</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31004</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.3146600000000001</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.39535</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.31249</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.30553</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.29895</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.29333</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.28684</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.28488</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.29594</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.29645</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31011</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39093</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43455</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35673</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.53028</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5356300000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.15027</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.85388</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.5669500000000001</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.74239</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.48846</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5956699999999999</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.52826</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.43732</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.71716</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.6633300000000001</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.10086</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.86481</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.73854</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.59773</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.40908</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32672</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.31469</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.30278</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.27597</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.28766</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.2814700000000001</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.29304</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.28411</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.29403</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.29406</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.29536</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.28122</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.28181</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.27528</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.2806</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.27127</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35339</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.29812</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29665</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.26012</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.42028</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.52601</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19763</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29528</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43465</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.49192</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.38973</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.43209</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36346</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.48932</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.43349</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.5304800000000001</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42907</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.4458</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.40273</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.46891</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.5739099999999999</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.3962</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.48833</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.41576</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.4269</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33853</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.30214</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.31816</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.71562</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.40167</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.46017</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.42885</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.41648</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.36385</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.37894</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.29661</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.26048</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.39236</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.4802</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30136</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35355</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.44918</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.46205</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.44565</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.4725</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37402</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38838</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.39967</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37533</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.36758</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.43208</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.5245299999999999</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.42472</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36931</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.44986</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.41689</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39585</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33334</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.38177</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36322</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.29342</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30356</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17618</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30433</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29594</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14584</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19877</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.1476</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28704</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04852</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12216</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22689</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26013</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14256</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14604</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28343</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18665</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22696</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27535</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.16127</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.17133</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30293</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20443</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.16703</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.29823</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.30523</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.39275</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.44246</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.39475</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.5638200000000001</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.41319</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.42635</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39781</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.44985</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40525</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.49095</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.4384</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.43307</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.47137</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.45114</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.44475</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.45694</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47452</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40694</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39286</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.36576</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38353</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38481</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36207</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36513</v>
       </c>
     </row>
   </sheetData>
